--- a/output/metrics_report.xlsx
+++ b/output/metrics_report.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28.57%</t>
+          <t>66.67%</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,51 @@
         <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>device.c</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>main.c</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>shared.h</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>18.4</t>
         </is>
@@ -586,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,51 +676,6 @@
         <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>device.c</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>main.c</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>shared.h</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>18.4</t>
         </is>
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,36 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>data.c</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>main.c</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
